--- a/public/plantillas/joyeria.xlsx
+++ b/public/plantillas/joyeria.xlsx
@@ -502,7 +502,7 @@
         <v>Anillo solitario diamante</v>
       </c>
       <c r="H2" t="str">
-        <v>Anillos</v>
+        <v>Joyería</v>
       </c>
       <c r="I2" t="str">
         <v>local</v>
@@ -561,7 +561,7 @@
         <v>Cadena básica 45cm</v>
       </c>
       <c r="H3" t="str">
-        <v>Cadenas</v>
+        <v>Joyería</v>
       </c>
       <c r="I3" t="str">
         <v>local</v>
